--- a/packages/testing-fixtures/assets/camil-management/04_Cronograma_Contratual_Amortizacoes.xlsx
+++ b/packages/testing-fixtures/assets/camil-management/04_Cronograma_Contratual_Amortizacoes.xlsx
@@ -398,7 +398,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K25"/>
+  <cols>
+    <col min="1" max="1" width="42.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="62.83203125" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
+    <col min="9" max="9" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,7 +420,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cronograma contratual de amortizações por série, ano safra (junho a maio), R$ mil; totais por ano iguais à nota 15 do ITR de 31/05/2026; alocação por série sintética</v>
+        <v>Cronograma contratual sintético de amortizações por série, ano safra (junho a maio), R$ mil; principal bruto reconciliado separadamente ao cronograma contábil da nota 15 do ITR de 31/05/2026</v>
       </c>
     </row>
     <row r="4">
@@ -459,16 +472,16 @@
         <v>gerencial (sintético)</v>
       </c>
       <c r="E5">
-        <v>666686</v>
+        <v>671334</v>
       </c>
       <c r="F5">
-        <v>421138</v>
+        <v>424074</v>
       </c>
       <c r="G5">
-        <v>143470</v>
+        <v>144470</v>
       </c>
       <c r="H5">
-        <v>74018</v>
+        <v>74534</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -477,7 +490,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1305312</v>
+        <v>1314412</v>
       </c>
     </row>
     <row r="6">
@@ -494,7 +507,7 @@
         <v>gerencial (sintético)</v>
       </c>
       <c r="E6">
-        <v>442943</v>
+        <v>442944</v>
       </c>
       <c r="F6">
         <v>279802</v>
@@ -535,7 +548,7 @@
         <v>17480</v>
       </c>
       <c r="G7">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="H7">
         <v>3072</v>
@@ -570,7 +583,7 @@
         <v>58448</v>
       </c>
       <c r="G8">
-        <v>19912</v>
+        <v>19911</v>
       </c>
       <c r="H8">
         <v>10273</v>
@@ -1007,7 +1020,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Custos de transação de debêntures</v>
+        <v>Principal contratual sintético</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1016,33 +1029,33 @@
         <v/>
       </c>
       <c r="D21" t="str">
-        <v>ITR nota 15</v>
+        <v>arquivos gerenciais sintéticos</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1234476</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>779804</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1229475</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>695013</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>994544</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>809198</v>
       </c>
       <c r="K21">
-        <v>-63224</v>
+        <v>5742510</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Total</v>
+        <v>Ajuste de bridge das linhas</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1051,33 +1064,138 @@
         <v/>
       </c>
       <c r="D22" t="str">
+        <v>custos de transação de 9.099 mais diferença de arredondamento de 1</v>
+      </c>
+      <c r="E22">
+        <v>-4648</v>
+      </c>
+      <c r="F22">
+        <v>-2936</v>
+      </c>
+      <c r="G22">
+        <v>-1000</v>
+      </c>
+      <c r="H22">
+        <v>-516</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-9100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Cronograma público da nota 15</v>
+      </c>
+      <c r="B23" t="str">
         <v/>
       </c>
-      <c r="E22">
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>ITR nota 15</v>
+      </c>
+      <c r="E23">
         <v>1229828</v>
       </c>
-      <c r="F22">
+      <c r="F23">
         <v>776868</v>
       </c>
-      <c r="G22">
+      <c r="G23">
         <v>1228475</v>
       </c>
-      <c r="H22">
+      <c r="H23">
         <v>694497</v>
       </c>
-      <c r="I22">
+      <c r="I23">
         <v>994544</v>
       </c>
-      <c r="J22">
+      <c r="J23">
         <v>809198</v>
       </c>
-      <c r="K22">
+      <c r="K23">
+        <v>5733410</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Custos de transação de debêntures</v>
+      </c>
+      <c r="B24" t="str">
+        <v/>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>ITR nota 15; não alocados por ano</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-63224</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Saldo contábil reconciliado</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>cronograma público menos custos de debêntures</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>5670186</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1085,6 +1203,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A4"/>
+  <cols>
+    <col min="1" max="1" width="120.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1093,7 +1214,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Amortizações parciais declaradas para caber nos totais do ITR</v>
+        <v>Amortizações parciais sintéticas usadas na alocação por série</v>
       </c>
     </row>
     <row r="3">
